--- a/docs/user-research/questionnaires/wave-1/wave-1_contact_list.xlsx
+++ b/docs/user-research/questionnaires/wave-1/wave-1_contact_list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dexter/DexterOS/products/Voliti/docs/user-research/questionnaires/cleaned/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dexter/DexterOS/products/Voliti/docs/user-research/questionnaires/wave-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A88C773-3E4C-CF43-910A-D8FD64CB7F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7FDC58-A94C-A04D-A7FC-E92784F742FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="待联系用户" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="196">
   <si>
     <t>ID</t>
   </si>
@@ -811,6 +811,21 @@
 【花费】三千到一万
 【坚持最久方法】各种都试过了，用过替尔泊肽和司美格鲁肽减重版（可能体质原因 一斤都没瘦 食欲也贼好）；用过日本的什么燃脂片也没用。
 【一句话感受】反正发现还是管住嘴迈开腿最管用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ivy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kaihong</t>
+  </si>
+  <si>
+    <t>Be Ran</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小丹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1618,6 +1633,9 @@
       <c r="C6" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="D6" s="2" t="s">
+        <v>192</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>88</v>
       </c>
@@ -1787,6 +1805,9 @@
       <c r="C8" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="D8" s="2" t="s">
+        <v>193</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>107</v>
       </c>
@@ -1861,6 +1882,9 @@
       <c r="C9" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="D9" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>112</v>
       </c>
@@ -2100,6 +2124,9 @@
       </c>
       <c r="C12" s="2" t="s">
         <v>31</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>195</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>133</v>
